--- a/powerflow instances/Random Demands.xlsx
+++ b/powerflow instances/Random Demands.xlsx
@@ -25,9 +25,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1">
-  <si>
-    <t>118_15</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>x6</t>
+  </si>
+  <si>
+    <t>x7</t>
+  </si>
+  <si>
+    <t>x8</t>
+  </si>
+  <si>
+    <t>x9</t>
+  </si>
+  <si>
+    <t>x10</t>
+  </si>
+  <si>
+    <t>x11</t>
+  </si>
+  <si>
+    <t>x12</t>
+  </si>
+  <si>
+    <t>x13</t>
+  </si>
+  <si>
+    <t>x14</t>
+  </si>
+  <si>
+    <t>x15</t>
+  </si>
+  <si>
+    <t>x16</t>
+  </si>
+  <si>
+    <t>x17</t>
+  </si>
+  <si>
+    <t>x18</t>
+  </si>
+  <si>
+    <t>x19</t>
+  </si>
+  <si>
+    <t>x20</t>
+  </si>
+  <si>
+    <t>x21</t>
+  </si>
+  <si>
+    <t>x22</t>
+  </si>
+  <si>
+    <t>x23</t>
+  </si>
+  <si>
+    <t>x24</t>
+  </si>
+  <si>
+    <t>x25</t>
+  </si>
+  <si>
+    <t>x26</t>
+  </si>
+  <si>
+    <t>x27</t>
+  </si>
+  <si>
+    <t>x28</t>
+  </si>
+  <si>
+    <t>x29</t>
+  </si>
+  <si>
+    <t>x30</t>
+  </si>
+  <si>
+    <t>x31</t>
+  </si>
+  <si>
+    <t>x32</t>
+  </si>
+  <si>
+    <t>x33</t>
+  </si>
+  <si>
+    <t>x34</t>
+  </si>
+  <si>
+    <t>x35</t>
+  </si>
+  <si>
+    <t>x36</t>
+  </si>
+  <si>
+    <t>x37</t>
+  </si>
+  <si>
+    <t>x38</t>
+  </si>
+  <si>
+    <t>x39</t>
+  </si>
+  <si>
+    <t>x40</t>
+  </si>
+  <si>
+    <t>x41</t>
+  </si>
+  <si>
+    <t>x42</t>
+  </si>
+  <si>
+    <t>x43</t>
+  </si>
+  <si>
+    <t>x44</t>
+  </si>
+  <si>
+    <t>x45</t>
+  </si>
+  <si>
+    <t>x46</t>
+  </si>
+  <si>
+    <t>x47</t>
+  </si>
+  <si>
+    <t>x48</t>
+  </si>
+  <si>
+    <t>x49</t>
+  </si>
+  <si>
+    <t>x50</t>
+  </si>
+  <si>
+    <t>x51</t>
+  </si>
+  <si>
+    <t>x52</t>
+  </si>
+  <si>
+    <t>x53</t>
+  </si>
+  <si>
+    <t>x54</t>
+  </si>
+  <si>
+    <t>x55</t>
+  </si>
+  <si>
+    <t>x56</t>
+  </si>
+  <si>
+    <t>x57</t>
+  </si>
+  <si>
+    <t>x58</t>
+  </si>
+  <si>
+    <t>x59</t>
+  </si>
+  <si>
+    <t>x60</t>
+  </si>
+  <si>
+    <t>x61</t>
+  </si>
+  <si>
+    <t>x62</t>
+  </si>
+  <si>
+    <t>x63</t>
+  </si>
+  <si>
+    <t>x64</t>
+  </si>
+  <si>
+    <t>x65</t>
+  </si>
+  <si>
+    <t>x66</t>
+  </si>
+  <si>
+    <t>x67</t>
+  </si>
+  <si>
+    <t>x68</t>
+  </si>
+  <si>
+    <t>x69</t>
+  </si>
+  <si>
+    <t>x70</t>
+  </si>
+  <si>
+    <t>x71</t>
+  </si>
+  <si>
+    <t>x72</t>
+  </si>
+  <si>
+    <t>x73</t>
+  </si>
+  <si>
+    <t>x74</t>
+  </si>
+  <si>
+    <t>x75</t>
+  </si>
+  <si>
+    <t>x76</t>
+  </si>
+  <si>
+    <t>x77</t>
+  </si>
+  <si>
+    <t>x78</t>
+  </si>
+  <si>
+    <t>x79</t>
+  </si>
+  <si>
+    <t>x80</t>
+  </si>
+  <si>
+    <t>x81</t>
+  </si>
+  <si>
+    <t>x82</t>
+  </si>
+  <si>
+    <t>x83</t>
+  </si>
+  <si>
+    <t>x84</t>
+  </si>
+  <si>
+    <t>x85</t>
+  </si>
+  <si>
+    <t>x86</t>
+  </si>
+  <si>
+    <t>x87</t>
+  </si>
+  <si>
+    <t>x88</t>
+  </si>
+  <si>
+    <t>x89</t>
+  </si>
+  <si>
+    <t>x90</t>
+  </si>
+  <si>
+    <t>x91</t>
+  </si>
+  <si>
+    <t>x92</t>
+  </si>
+  <si>
+    <t>x93</t>
+  </si>
+  <si>
+    <t>x94</t>
+  </si>
+  <si>
+    <t>x95</t>
+  </si>
+  <si>
+    <t>x96</t>
+  </si>
+  <si>
+    <t>x97</t>
+  </si>
+  <si>
+    <t>x98</t>
+  </si>
+  <si>
+    <t>x99</t>
+  </si>
+  <si>
+    <t>x100</t>
+  </si>
+  <si>
+    <t>x101</t>
+  </si>
+  <si>
+    <t>x102</t>
+  </si>
+  <si>
+    <t>x103</t>
+  </si>
+  <si>
+    <t>x104</t>
+  </si>
+  <si>
+    <t>x105</t>
+  </si>
+  <si>
+    <t>x106</t>
+  </si>
+  <si>
+    <t>x107</t>
+  </si>
+  <si>
+    <t>x108</t>
+  </si>
+  <si>
+    <t>x109</t>
+  </si>
+  <si>
+    <t>x110</t>
+  </si>
+  <si>
+    <t>x111</t>
+  </si>
+  <si>
+    <t>x112</t>
+  </si>
+  <si>
+    <t>x113</t>
+  </si>
+  <si>
+    <t>x114</t>
+  </si>
+  <si>
+    <t>x115</t>
+  </si>
+  <si>
+    <t>x116</t>
+  </si>
+  <si>
+    <t>x117</t>
+  </si>
+  <si>
+    <t>x118</t>
   </si>
 </sst>
 </file>
@@ -379,601 +730,718 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:A119"/>
+  <dimension ref="A1:DN2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:118">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:118">
       <c r="A2">
         <v>0.56</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3">
+      <c r="B2">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4">
+      <c r="C2">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5">
+      <c r="D2">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7">
+      <c r="E2">
+        <v>0.0</v>
+      </c>
+      <c r="F2">
         <v>0.59</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8">
+      <c r="G2">
         <v>0.29</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9">
+      <c r="H2">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12">
+      <c r="I2">
+        <v>0.0</v>
+      </c>
+      <c r="J2">
+        <v>0.0</v>
+      </c>
+      <c r="K2">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13">
+      <c r="L2">
         <v>0.56</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14">
+      <c r="M2">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15">
+      <c r="N2">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16">
+      <c r="O2">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17">
+      <c r="P2">
         <v>0.37</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18">
+      <c r="Q2">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19">
+      <c r="R2">
         <v>0.6900000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20">
+      <c r="S2">
         <v>0.56</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21">
+      <c r="T2">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22">
+      <c r="U2">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23">
+      <c r="V2">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24">
+      <c r="W2">
         <v>0.07</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25">
+      <c r="X2">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28">
+      <c r="Y2">
+        <v>0.0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0</v>
+      </c>
+      <c r="AA2">
         <v>0.8300000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29">
+      <c r="AB2">
         <v>0.31</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30">
+      <c r="AC2">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32">
+      <c r="AD2">
+        <v>0.0</v>
+      </c>
+      <c r="AE2">
         <v>0.47000000000000003</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33">
+      <c r="AF2">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34">
+      <c r="AG2">
         <v>0.29</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35">
+      <c r="AH2">
         <v>0.71</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36">
+      <c r="AI2">
         <v>0.35000000000000003</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37">
+      <c r="AJ2">
         <v>0.32</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40">
+      <c r="AK2">
+        <v>0.0</v>
+      </c>
+      <c r="AL2">
+        <v>0.0</v>
+      </c>
+      <c r="AM2">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41">
+      <c r="AN2">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42">
+      <c r="AO2">
         <v>0.48</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43">
+      <c r="AP2">
         <v>1.11</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44">
+      <c r="AQ2">
         <v>0.31</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45">
+      <c r="AR2">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46">
+      <c r="AS2">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47">
+      <c r="AT2">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48">
+      <c r="AU2">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49">
+      <c r="AV2">
         <v>0.35000000000000003</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50">
+      <c r="AW2">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51">
+      <c r="AX2">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52">
+      <c r="AY2">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53">
+      <c r="AZ2">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54">
+      <c r="BA2">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55">
+      <c r="BB2">
         <v>1.24</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56">
+      <c r="BC2">
         <v>0.7000000000000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57">
+      <c r="BD2">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58">
+      <c r="BE2">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59">
+      <c r="BF2">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60">
+      <c r="BG2">
         <v>2.7800000000000002</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61">
+      <c r="BH2">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63">
+      <c r="BI2">
+        <v>0.0</v>
+      </c>
+      <c r="BJ2">
         <v>0.8300000000000001</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67">
+      <c r="BK2">
+        <v>0.0</v>
+      </c>
+      <c r="BL2">
+        <v>0.0</v>
+      </c>
+      <c r="BM2">
+        <v>0.0</v>
+      </c>
+      <c r="BN2">
         <v>0.47000000000000003</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68">
+      <c r="BO2">
         <v>0.41000000000000003</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71">
+      <c r="BP2">
+        <v>0.0</v>
+      </c>
+      <c r="BQ2">
+        <v>0.0</v>
+      </c>
+      <c r="BR2">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73">
+      <c r="BS2">
+        <v>0.0</v>
+      </c>
+      <c r="BT2">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74">
+      <c r="BU2">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75">
+      <c r="BV2">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76">
+      <c r="BW2">
         <v>0.47000000000000003</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77">
+      <c r="BX2">
         <v>0.72</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78">
+      <c r="BY2">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79">
+      <c r="BZ2">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80">
+      <c r="CA2">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81">
+      <c r="CB2">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83">
+      <c r="CC2">
+        <v>0.0</v>
+      </c>
+      <c r="CD2">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84">
+      <c r="CE2">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85">
+      <c r="CF2">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86">
+      <c r="CG2">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87">
+      <c r="CH2">
         <v>0.32</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89">
+      <c r="CI2">
+        <v>0.0</v>
+      </c>
+      <c r="CJ2">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91">
+      <c r="CK2">
+        <v>0.0</v>
+      </c>
+      <c r="CL2">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92">
+      <c r="CM2">
         <v>0.19</v>
       </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93">
+      <c r="CN2">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94">
+      <c r="CO2">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95">
+      <c r="CP2">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96">
+      <c r="CQ2">
         <v>0.44</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97">
+      <c r="CR2">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98">
+      <c r="CS2">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99">
+      <c r="CT2">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100">
+      <c r="CU2">
         <v>0.5700000000000001</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101">
+      <c r="CV2">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102">
+      <c r="CW2">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103">
+      <c r="CX2">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104">
+      <c r="CY2">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105">
+      <c r="CZ2">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106">
+      <c r="DA2">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107">
+      <c r="DB2">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108">
+      <c r="DC2">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109">
+      <c r="DD2">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110">
+      <c r="DE2">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111">
+      <c r="DF2">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113">
+      <c r="DG2">
+        <v>0.0</v>
+      </c>
+      <c r="DH2">
         <v>0.73</v>
       </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114">
+      <c r="DI2">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115">
+      <c r="DJ2">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116">
+      <c r="DK2">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117">
+      <c r="DL2">
         <v>1.99</v>
       </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118">
+      <c r="DM2">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119">
+      <c r="DN2">
         <v>0.42</v>
       </c>
     </row>
